--- a/Result/profitability/2455.xlsx
+++ b/Result/profitability/2455.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.46</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.79375</v>
       </c>
       <c r="N2" t="n">
-        <v>36.28125</v>
+        <v>35.98</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.65125</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>33.86125000000001</v>
+        <v>34.18625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5825</v>
+        <v>0.62</v>
       </c>
       <c r="N4" t="n">
-        <v>32.83</v>
+        <v>32.66875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.39</v>
+        <v>0.50875</v>
       </c>
       <c r="N5" t="n">
-        <v>29.4225</v>
+        <v>29.95</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.38</v>
+        <v>0.41625</v>
       </c>
       <c r="N6" t="n">
-        <v>27.63875</v>
+        <v>28.3575</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.74</v>
       </c>
       <c r="M7" t="n">
-        <v>0.365</v>
+        <v>0.3775000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>27.98625</v>
+        <v>28.15375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.11</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3725000000000001</v>
+        <v>0.38375</v>
       </c>
       <c r="N8" t="n">
-        <v>28.525</v>
+        <v>28.59</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>965</v>
+      </c>
+      <c r="D75" t="n">
+        <v>593</v>
+      </c>
+      <c r="E75" t="n">
+        <v>373</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="G75" t="n">
+        <v>224</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>23.18%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>237</v>
+      </c>
+      <c r="K75" t="n">
+        <v>214</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.83375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>37.26875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08999999999999986</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.08490566037735836</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.519999999999996</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01365187713310578</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.749999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.219999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1227100901424834</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
